--- a/Lab_4/data/partB/param_optimization_process/v150_k40_s150_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v150_k40_s150_results.xlsx
@@ -518,49 +518,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2</v>
-      </c>
       <c r="I2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -573,19 +573,19 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -594,13 +594,13 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -609,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -646,22 +646,22 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -677,46 +677,46 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F5" t="n">
         <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="n">
-        <v>6</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
       <c r="P5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -729,28 +729,28 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
         <v>2</v>
       </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3</v>
-      </c>
       <c r="F6" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G6" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -759,16 +759,16 @@
         <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -790,16 +790,16 @@
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -808,19 +808,19 @@
         <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -842,34 +842,34 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" t="n">
         <v>5</v>
       </c>
-      <c r="G8" t="n">
-        <v>16</v>
-      </c>
-      <c r="H8" t="n">
-        <v>9</v>
-      </c>
       <c r="I8" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
@@ -894,37 +894,37 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="n">
         <v>4</v>
       </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -937,13 +937,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -955,25 +955,25 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -1001,25 +1001,25 @@
         <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H11" t="n">
         <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
         <v>2</v>
@@ -1028,7 +1028,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1047,10 +1047,10 @@
         <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1062,13 +1062,13 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
         <v>7</v>
@@ -1114,22 +1114,22 @@
         <v>7</v>
       </c>
       <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
         <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
         <v>4</v>
@@ -1151,40 +1151,40 @@
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G14" t="n">
         <v>7</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="O14" t="n">
         <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -1200,16 +1200,16 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1218,22 +1218,22 @@
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1249,46 +1249,46 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
         <v>2</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="n">
         <v>1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6520,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7455,7 +7455,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7778,7 +7778,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7982,7 +7982,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9393,7 +9393,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10617,7 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10923,7 +10923,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11110,7 +11110,7 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11620,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12368,7 +12368,7 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12487,7 +12487,7 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12504,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12555,7 +12555,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12691,7 +12691,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12827,7 +12827,7 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12963,7 +12963,7 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -12997,7 +12997,7 @@
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13048,7 +13048,7 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13201,7 +13201,7 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13235,7 +13235,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13303,7 +13303,7 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13422,7 +13422,7 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13813,7 +13813,7 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14238,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14442,7 +14442,7 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14544,7 +14544,7 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -15003,7 +15003,7 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15054,7 +15054,7 @@
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15241,7 +15241,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -15377,7 +15377,7 @@
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15428,7 +15428,7 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15479,7 +15479,7 @@
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15513,7 +15513,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15632,7 +15632,7 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -15700,7 +15700,7 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15819,7 +15819,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -16057,7 +16057,7 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16176,7 +16176,7 @@
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16210,7 +16210,7 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16363,7 +16363,7 @@
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16397,7 +16397,7 @@
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16448,7 +16448,7 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16618,7 +16618,7 @@
       </c>
       <c r="C901" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16771,7 +16771,7 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16890,7 +16890,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -16924,7 +16924,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17196,7 +17196,7 @@
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17230,7 +17230,7 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17264,7 +17264,7 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17315,7 +17315,7 @@
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17536,7 +17536,7 @@
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17740,7 +17740,7 @@
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17859,7 +17859,7 @@
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17876,7 +17876,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -17961,7 +17961,7 @@
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17995,7 +17995,7 @@
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -18080,7 +18080,7 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="C994" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18386,7 @@
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -18454,7 +18454,7 @@
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18505,7 +18505,7 @@
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -18556,7 +18556,7 @@
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18573,7 +18573,7 @@
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18641,7 +18641,7 @@
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18692,7 +18692,7 @@
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19083,7 +19083,7 @@
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19117,7 +19117,7 @@
       </c>
       <c r="C1048" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19134,7 +19134,7 @@
       </c>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19253,7 +19253,7 @@
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19287,7 +19287,7 @@
       </c>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19355,7 +19355,7 @@
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19627,7 +19627,7 @@
       </c>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19644,7 +19644,7 @@
       </c>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19712,7 +19712,7 @@
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19797,7 +19797,7 @@
       </c>
       <c r="C1088" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="C1089" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19916,7 +19916,7 @@
       </c>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -19967,7 +19967,7 @@
       </c>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20137,7 +20137,7 @@
       </c>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20409,7 +20409,7 @@
       </c>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20443,7 +20443,7 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20681,7 +20681,7 @@
       </c>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20715,7 +20715,7 @@
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20732,7 +20732,7 @@
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20970,7 +20970,7 @@
       </c>
       <c r="C1157" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21038,7 +21038,7 @@
       </c>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21225,7 +21225,7 @@
       </c>
       <c r="C1172" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21310,7 +21310,7 @@
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -21412,7 +21412,7 @@
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21514,7 +21514,7 @@
       </c>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21684,7 +21684,7 @@
       </c>
       <c r="C1199" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -21701,7 +21701,7 @@
       </c>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21752,7 +21752,7 @@
       </c>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21786,7 +21786,7 @@
       </c>
       <c r="C1205" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21939,7 +21939,7 @@
       </c>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21956,7 +21956,7 @@
       </c>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22058,7 +22058,7 @@
       </c>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -22075,7 +22075,7 @@
       </c>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22143,7 +22143,7 @@
       </c>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22194,7 +22194,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22330,7 +22330,7 @@
       </c>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22449,7 +22449,7 @@
       </c>
       <c r="C1244" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22483,7 +22483,7 @@
       </c>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22789,7 +22789,7 @@
       </c>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -22840,7 +22840,7 @@
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22857,7 +22857,7 @@
       </c>
       <c r="C1268" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22891,7 +22891,7 @@
       </c>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23044,7 +23044,7 @@
       </c>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -23180,7 +23180,7 @@
       </c>
       <c r="C1287" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23197,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23316,7 +23316,7 @@
       </c>
       <c r="C1295" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23928,7 +23928,7 @@
       </c>
       <c r="C1331" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24013,7 +24013,7 @@
       </c>
       <c r="C1336" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24047,7 +24047,7 @@
       </c>
       <c r="C1338" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24302,7 +24302,7 @@
       </c>
       <c r="C1353" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24523,7 +24523,7 @@
       </c>
       <c r="C1366" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24812,7 +24812,7 @@
       </c>
       <c r="C1383" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24982,7 +24982,7 @@
       </c>
       <c r="C1393" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25016,7 @@
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25101,7 +25101,7 @@
       </c>
       <c r="C1400" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25118,7 +25118,7 @@
       </c>
       <c r="C1401" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25152,7 +25152,7 @@
       </c>
       <c r="C1403" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25169,7 +25169,7 @@
       </c>
       <c r="C1404" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
       </c>
       <c r="C1411" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25373,7 +25373,7 @@
       </c>
       <c r="C1416" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25628,7 +25628,7 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25696,7 +25696,7 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="C1440" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -25798,7 +25798,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25951,7 +25951,7 @@
       </c>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25985,7 +25985,7 @@
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26019,7 +26019,7 @@
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26104,7 +26104,7 @@
       </c>
       <c r="C1459" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26138,7 +26138,7 @@
       </c>
       <c r="C1461" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26240,7 +26240,7 @@
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -26308,7 +26308,7 @@
       </c>
       <c r="C1471" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26410,7 @@
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26427,7 +26427,7 @@
       </c>
       <c r="C1478" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="C1482" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26529,7 +26529,7 @@
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26546,7 +26546,7 @@
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -26580,7 +26580,7 @@
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="C1488" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26614,7 +26614,7 @@
       </c>
       <c r="C1489" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26733,7 +26733,7 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26750,7 +26750,7 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26767,7 +26767,7 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26801,7 +26801,7 @@
       </c>
       <c r="C1500" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
